--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationadministrationBase.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationadministrationBase.xlsx
@@ -449,7 +449,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.extension:requestDepartment</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationadministrationBase.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationadministrationBase.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -268,7 +268,7 @@
     <t>患者への薬剤投与記録</t>
   </si>
   <si>
-    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的なEncounter（診察、受診、入退院など）と結びつけます。</t>
+    <t>患者が薬剤を服用する、あるいは投与される事象を説明します。これは、錠剤を飲むだけだったり、長時間の点滴だったりすることがあります。関連するリソースは、この事象を許可された処方箋や、患者と医療従事者の具体的な受療行動と結びつけます。</t>
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -702,7 +702,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -796,7 +796,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -893,7 +893,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -955,7 +955,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -979,7 +979,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -989,7 +989,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>医薬品</t>
@@ -1009,7 +1009,7 @@
     <t>投与可能な物質または製品を識別するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1027,7 +1027,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1052,7 +1052,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1187,7 +1187,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1199,7 +1199,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1227,7 +1227,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1242,7 +1242,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1270,7 +1270,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1295,7 +1295,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1383,7 +1383,7 @@
     <t>薬剤が体内に入るか、体表面に塗布される場所を示すコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1404,7 +1404,7 @@
     <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1428,7 +1428,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1440,7 +1440,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1463,7 +1463,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>時間当たりの投与量</t>
@@ -1484,7 +1484,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1804,17 +1804,17 @@
   <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.53515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.1484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.3828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.1796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="16.4140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.76953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.39453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1823,27 +1823,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.77734375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="45.6171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.921875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="101.08984375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="22.50390625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="86.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="19.29296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationadministrationBase.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationadministrationBase.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
